--- a/24V_BOM.xlsx
+++ b/24V_BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bobbystyles/Desktop/24V-24V-Converter/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bobbystyles/Desktop/MRC/Git/24v-24v-converter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C80771-69EC-5A42-A6DA-97D4ADD819CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCCCAAA-5159-E84F-A0A9-058986283C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="860" windowWidth="28600" windowHeight="17820" xr2:uid="{62C9FD8D-305F-FF42-B2BA-6BE6B3EFB71A}"/>
   </bookViews>
@@ -71,9 +71,6 @@
     <t>U1</t>
   </si>
   <si>
-    <t>Cbulk</t>
-  </si>
-  <si>
     <t>Cvcc</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
     <t>Ccs</t>
   </si>
   <si>
-    <t>Cin</t>
-  </si>
-  <si>
     <t>M4</t>
   </si>
   <si>
@@ -96,9 +90,6 @@
   </si>
   <si>
     <t>Cslope</t>
-  </si>
-  <si>
-    <t>Cout</t>
   </si>
   <si>
     <t>Css</t>
@@ -465,9 +456,6 @@
     <t>Cboot1/Cboot2</t>
   </si>
   <si>
-    <t>Coutx2/Coutx/Coutx3</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.digikey.com/en/products/detail/panasonic-industry/50SVPF10M/4209237?s=N4IgTCBcDaIKwAYDKA1ACgMQIwILIgF0BfIA  </t>
   </si>
   <si>
@@ -493,6 +481,20 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/RMCF0603FT64K9/1760863</t>
+  </si>
+  <si>
+    <t>C13-C18</t>
+  </si>
+  <si>
+    <t>C1-C7</t>
+  </si>
+  <si>
+    <t>C8-12
+C19-C23
+C24-C28</t>
+  </si>
+  <si>
+    <t>C29-C31</t>
   </si>
 </sst>
 </file>
@@ -598,7 +600,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -625,10 +627,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1004,133 +1003,133 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>56</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4.68</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4.68</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G5" s="14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>3</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="16" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="14">
-        <v>1</v>
-      </c>
-      <c r="D2" s="14">
-        <v>3</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="16" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="14">
-        <v>4</v>
-      </c>
-      <c r="D3" s="14">
-        <v>56</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G3" s="17"/>
-    </row>
-    <row r="4" spans="1:7" s="16" customFormat="1" ht="38" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="14">
-        <v>2</v>
-      </c>
-      <c r="D4" s="14">
-        <v>4.68</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="1:7" s="16" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="14">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14">
-        <v>4.68</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="16" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="14">
-        <v>1</v>
-      </c>
-      <c r="D6" s="14">
-        <v>3</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -1138,7 +1137,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C7" s="5">
         <v>1</v>
@@ -1147,10 +1146,10 @@
         <v>4.68</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G7" s="13"/>
     </row>
@@ -1159,7 +1158,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="5">
         <v>2</v>
@@ -1168,10 +1167,10 @@
         <v>6.75</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G8" s="13"/>
     </row>
@@ -1180,7 +1179,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
@@ -1189,31 +1188,31 @@
         <v>6.75</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C10" s="5">
         <v>2</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G10" s="13"/>
     </row>
@@ -1222,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
@@ -1231,10 +1230,10 @@
         <v>43.16</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G11" s="13"/>
     </row>
@@ -1243,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C12" s="5">
         <v>1</v>
@@ -1252,10 +1251,10 @@
         <v>11.7</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G12" s="13"/>
     </row>
@@ -1264,7 +1263,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
@@ -1274,39 +1273,39 @@
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G13" s="13"/>
     </row>
-    <row r="14" spans="1:7" s="16" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="14">
+    <row r="14" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="5">
         <v>7</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="5">
         <v>73.959999999999994</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>77</v>
+      <c r="E14" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>148</v>
+        <v>138</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C15" s="5">
         <v>1</v>
@@ -1315,40 +1314,40 @@
         <v>4.68</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G15" s="13"/>
     </row>
     <row r="16" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" s="5">
         <v>1</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:7" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C17" s="5">
         <v>1</v>
@@ -1357,19 +1356,19 @@
         <v>4.68</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G17" s="13"/>
     </row>
     <row r="18" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>14</v>
+        <v>147</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C18" s="5">
         <v>6</v>
@@ -1378,19 +1377,19 @@
         <v>106.09</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G18" s="13"/>
     </row>
     <row r="19" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C19" s="5">
         <v>1</v>
@@ -1399,19 +1398,19 @@
         <v>31.92</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G19" s="13"/>
     </row>
     <row r="20" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C20" s="5">
         <v>2</v>
@@ -1420,19 +1419,19 @@
         <v>31.92</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C21" s="5">
         <v>1</v>
@@ -1441,19 +1440,19 @@
         <v>4.68</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C22" s="5">
         <v>1</v>
@@ -1462,19 +1461,19 @@
         <v>4.68</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>19</v>
+      <c r="A23" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C23" s="5">
         <v>3</v>
@@ -1483,19 +1482,19 @@
         <v>106.09</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C24" s="5">
         <v>1</v>
@@ -1504,214 +1503,214 @@
         <v>6.75</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="13"/>
+    </row>
+    <row r="25" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5">
+        <v>3</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="5">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5">
+        <v>6.75</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="13"/>
+    </row>
+    <row r="27" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="5">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5">
+        <v>4.68</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="13"/>
-    </row>
-    <row r="25" spans="1:7" s="16" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A25" s="14" t="s">
+      <c r="G27" s="13"/>
+    </row>
+    <row r="28" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B28" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="14">
-        <v>1</v>
-      </c>
-      <c r="D25" s="14">
+      <c r="C28" s="5">
+        <v>1</v>
+      </c>
+      <c r="D28" s="5">
+        <v>4.68</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" s="13"/>
+    </row>
+    <row r="29" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5">
+        <v>4.68</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" s="13"/>
+    </row>
+    <row r="30" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1</v>
+      </c>
+      <c r="D30" s="5">
         <v>3</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="16" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A26" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="14">
-        <v>1</v>
-      </c>
-      <c r="D26" s="14">
+      <c r="E30" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="5">
+        <v>15</v>
+      </c>
+      <c r="D31" s="5">
         <v>6.75</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="G26" s="17"/>
-    </row>
-    <row r="27" spans="1:7" s="16" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A27" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="14" t="s">
+      <c r="E31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" s="13"/>
+    </row>
+    <row r="32" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C32" s="5">
+        <v>1</v>
+      </c>
+      <c r="D32" s="5">
         <v>4.68</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E32" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F32" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G27" s="17"/>
-    </row>
-    <row r="28" spans="1:7" s="16" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="14" t="s">
+      <c r="G32" s="13"/>
+    </row>
+    <row r="33" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>4.68</v>
-      </c>
-      <c r="E28" s="14" t="s">
+      <c r="C33" s="5">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5">
+        <v>3</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G28" s="17"/>
-    </row>
-    <row r="29" spans="1:7" s="16" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A29" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>4.68</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G29" s="17"/>
-    </row>
-    <row r="30" spans="1:7" s="16" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>3</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="16" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A31" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="14">
-        <v>15</v>
-      </c>
-      <c r="D31" s="14">
-        <v>6.75</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G31" s="17"/>
-    </row>
-    <row r="32" spans="1:7" s="16" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="14">
-        <v>1</v>
-      </c>
-      <c r="D32" s="14">
-        <v>4.68</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G32" s="17"/>
-    </row>
-    <row r="33" spans="1:7" s="16" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A33" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="14">
-        <v>1</v>
-      </c>
-      <c r="D33" s="14">
-        <v>3</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>150</v>
+      <c r="G33" s="14" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C34" s="5">
         <v>1</v>
@@ -1720,50 +1719,50 @@
         <v>4.68</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G34" s="13"/>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>132</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>135</v>
       </c>
       <c r="C35" s="5">
         <v>3</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C36" s="7">
         <v>2</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G36" s="13"/>
     </row>

--- a/24V_BOM.xlsx
+++ b/24V_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bobbystyles/Desktop/MRC/Git/24v-24v-converter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCCCAAA-5159-E84F-A0A9-058986283C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C37771E-19DA-3245-92F8-2157DE367844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="860" windowWidth="28600" windowHeight="17820" xr2:uid="{62C9FD8D-305F-FF42-B2BA-6BE6B3EFB71A}"/>
   </bookViews>
@@ -56,12 +56,6 @@
     <t>Rpg</t>
   </si>
   <si>
-    <t>Ccomp</t>
-  </si>
-  <si>
-    <t>Ccomp2</t>
-  </si>
-  <si>
     <t>Rsense</t>
   </si>
   <si>
@@ -495,6 +489,12 @@
   </si>
   <si>
     <t>C29-C31</t>
+  </si>
+  <si>
+    <t>C32, C33</t>
+  </si>
+  <si>
+    <t>C34</t>
   </si>
 </sst>
 </file>
@@ -1003,22 +1003,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="34" x14ac:dyDescent="0.2">
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
@@ -1035,21 +1035,21 @@
         <v>3</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="5">
         <v>4</v>
@@ -1058,19 +1058,19 @@
         <v>56</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4" s="5">
         <v>2</v>
@@ -1079,10 +1079,10 @@
         <v>4.68</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G4" s="13"/>
     </row>
@@ -1091,7 +1091,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" s="5">
         <v>1</v>
@@ -1100,13 +1100,13 @@
         <v>4.68</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="34" x14ac:dyDescent="0.2">
@@ -1114,7 +1114,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="5">
         <v>1</v>
@@ -1123,13 +1123,13 @@
         <v>3</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -1137,7 +1137,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" s="5">
         <v>1</v>
@@ -1146,19 +1146,19 @@
         <v>4.68</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>5</v>
+        <v>149</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="5">
         <v>2</v>
@@ -1167,19 +1167,19 @@
         <v>6.75</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
@@ -1188,40 +1188,40 @@
         <v>6.75</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C10" s="5">
         <v>2</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G10" s="13"/>
     </row>
     <row r="11" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
@@ -1230,19 +1230,19 @@
         <v>43.16</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G11" s="13"/>
     </row>
     <row r="12" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C12" s="5">
         <v>1</v>
@@ -1251,19 +1251,19 @@
         <v>11.7</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G12" s="13"/>
     </row>
     <row r="13" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
@@ -1273,16 +1273,16 @@
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G13" s="13"/>
     </row>
     <row r="14" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C14" s="5">
         <v>7</v>
@@ -1291,21 +1291,21 @@
         <v>73.959999999999994</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="5">
         <v>1</v>
@@ -1314,40 +1314,40 @@
         <v>4.68</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G15" s="13"/>
     </row>
     <row r="16" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C16" s="5">
         <v>1</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:7" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C17" s="5">
         <v>1</v>
@@ -1356,19 +1356,19 @@
         <v>4.68</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G17" s="13"/>
     </row>
     <row r="18" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C18" s="5">
         <v>6</v>
@@ -1377,19 +1377,19 @@
         <v>106.09</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G18" s="13"/>
     </row>
     <row r="19" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C19" s="5">
         <v>1</v>
@@ -1398,19 +1398,19 @@
         <v>31.92</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G19" s="13"/>
     </row>
     <row r="20" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C20" s="5">
         <v>2</v>
@@ -1419,19 +1419,19 @@
         <v>31.92</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C21" s="5">
         <v>1</v>
@@ -1440,19 +1440,19 @@
         <v>4.68</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22" s="5">
         <v>1</v>
@@ -1461,19 +1461,19 @@
         <v>4.68</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="5">
         <v>3</v>
@@ -1482,19 +1482,19 @@
         <v>106.09</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" s="5">
         <v>1</v>
@@ -1503,19 +1503,19 @@
         <v>6.75</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G24" s="13"/>
     </row>
     <row r="25" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" s="5">
         <v>1</v>
@@ -1524,21 +1524,21 @@
         <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C26" s="5">
         <v>1</v>
@@ -1547,19 +1547,19 @@
         <v>6.75</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G26" s="13"/>
     </row>
     <row r="27" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C27" s="5">
         <v>1</v>
@@ -1568,19 +1568,19 @@
         <v>4.68</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G27" s="13"/>
     </row>
     <row r="28" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C28" s="5">
         <v>1</v>
@@ -1589,19 +1589,19 @@
         <v>4.68</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G28" s="13"/>
     </row>
     <row r="29" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C29" s="5">
         <v>1</v>
@@ -1610,19 +1610,19 @@
         <v>4.68</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G29" s="13"/>
     </row>
     <row r="30" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C30" s="5">
         <v>1</v>
@@ -1631,21 +1631,21 @@
         <v>3</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C31" s="5">
         <v>15</v>
@@ -1654,19 +1654,19 @@
         <v>6.75</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G31" s="13"/>
     </row>
     <row r="32" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C32" s="5">
         <v>1</v>
@@ -1675,19 +1675,19 @@
         <v>4.68</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G32" s="13"/>
     </row>
     <row r="33" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C33" s="5">
         <v>1</v>
@@ -1696,21 +1696,21 @@
         <v>3</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C34" s="5">
         <v>1</v>
@@ -1719,50 +1719,50 @@
         <v>4.68</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G34" s="13"/>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C35" s="5">
         <v>3</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C36" s="7">
         <v>2</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G36" s="13"/>
     </row>
